--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemSubStatData.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemSubStatData.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>skillRangeFlat</t>
+          <t>skillRangePercent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,6 +1004,13 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>skillRangePercent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
